--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9871697425842285</v>
+        <v>0.7616684436798096</v>
       </c>
       <c r="E2" t="n">
         <v>0.9866574217406261</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.597283363342285</v>
+        <v>1.196430683135986</v>
       </c>
       <c r="E3" t="n">
         <v>0.9907112896519678</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9871697425842285</v>
+        <v>0.7616684436798096</v>
       </c>
       <c r="E2" t="n">
         <v>0.9866574217406261</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.597283363342285</v>
+        <v>1.196430683135986</v>
       </c>
       <c r="E3" t="n">
         <v>0.9907112896519678</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7616684436798096</v>
+        <v>0.5624017715454102</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9866574217406261</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9745507805678763</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9870129870129871</v>
+        <v>0.99375</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.196430683135986</v>
+        <v>0.822310209274292</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9907112896519678</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9745507805678763</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9870129870129871</v>
+        <v>0.99375</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7616684436798096</v>
+        <v>0.5624017715454102</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9866574217406261</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9745507805678763</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9870129870129871</v>
+        <v>0.99375</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.196430683135986</v>
+        <v>0.822310209274292</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9907112896519678</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9745507805678763</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9870129870129871</v>
+        <v>0.99375</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5624017715454102</v>
+        <v>0.666132926940918</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8057897569798677</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.7891156462585034</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7758159963014333</v>
       </c>
       <c r="H2" t="n">
-        <v>0.99375</v>
+        <v>0.9142429080475727</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.822310209274292</v>
+        <v>1.085041999816895</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.8123478482222627</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.7687074829931972</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7340136023146615</v>
       </c>
       <c r="H3" t="n">
-        <v>0.99375</v>
+        <v>0.928496228423342</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.03236722946167</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8051177669356531</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8027210884353742</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7415815671097846</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9041603035772131</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 2, 'min_samples_split': 10}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5624017715454102</v>
+        <v>0.666132926940918</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8057897569798677</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.7891156462585034</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7758159963014333</v>
       </c>
       <c r="H2" t="n">
-        <v>0.99375</v>
+        <v>0.9142429080475727</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.822310209274292</v>
+        <v>1.085041999816895</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.8123478482222627</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.7687074829931972</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7340136023146615</v>
       </c>
       <c r="H3" t="n">
-        <v>0.99375</v>
+        <v>0.928496228423342</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.03236722946167</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8051177669356531</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8027210884353742</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7415815671097846</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9041603035772131</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 2, 'min_samples_split': 10}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.666132926940918</v>
+        <v>1.825597286224365</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8057897569798677</v>
+        <v>0.9085511310346576</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7891156462585034</v>
+        <v>0.9246260069044879</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7758159963014333</v>
+        <v>0.8979170281613919</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9142429080475727</v>
+        <v>0.9514865145603006</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.085041999816895</v>
+        <v>4.178443670272827</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8123478482222627</v>
+        <v>0.9056173787944439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7687074829931972</v>
+        <v>0.9286536248561565</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7340136023146615</v>
+        <v>0.9023524720893141</v>
       </c>
       <c r="H3" t="n">
-        <v>0.928496228423342</v>
+        <v>0.9010477635667318</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.03236722946167</v>
+        <v>6.760910749435425</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8051177669356531</v>
+        <v>0.9122842474999594</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8027210884353742</v>
+        <v>0.9346950517836594</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7415815671097846</v>
+        <v>0.9108030306884048</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9041603035772131</v>
+        <v>0.9103033094876798</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 2, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.666132926940918</v>
+        <v>1.825597286224365</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8057897569798677</v>
+        <v>0.9085511310346576</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7891156462585034</v>
+        <v>0.9246260069044879</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7758159963014333</v>
+        <v>0.8979170281613919</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9142429080475727</v>
+        <v>0.9514865145603006</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -692,23 +692,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.085041999816895</v>
+        <v>4.178443670272827</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8123478482222627</v>
+        <v>0.9056173787944439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7687074829931972</v>
+        <v>0.9286536248561565</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7340136023146615</v>
+        <v>0.9023524720893141</v>
       </c>
       <c r="H3" t="n">
-        <v>0.928496228423342</v>
+        <v>0.9010477635667318</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -727,23 +727,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.03236722946167</v>
+        <v>6.760910749435425</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8051177669356531</v>
+        <v>0.9122842474999594</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8027210884353742</v>
+        <v>0.9346950517836594</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7415815671097846</v>
+        <v>0.9108030306884048</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9041603035772131</v>
+        <v>0.9103033094876798</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 2, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.825597286224365</v>
+        <v>0.4692773818969727</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9085511310346576</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9246260069044879</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8979170281613919</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9514865145603006</v>
+        <v>0.99375</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4.178443670272827</v>
+        <v>0.7205154895782471</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9056173787944439</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9286536248561565</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9023524720893141</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9010477635667318</v>
+        <v>0.99375</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6.760910749435425</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9122842474999594</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9346950517836594</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9108030306884048</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9103033094876798</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.825597286224365</v>
+        <v>0.4692773818969727</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9085511310346576</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9246260069044879</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8979170281613919</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9514865145603006</v>
+        <v>0.99375</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4.178443670272827</v>
+        <v>0.7205154895782471</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9056173787944439</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9286536248561565</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9023524720893141</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9010477635667318</v>
+        <v>0.99375</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6.760910749435425</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9122842474999594</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9346950517836594</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9108030306884048</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9103033094876798</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4692773818969727</v>
+        <v>0.461101770401001</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7205154895782471</v>
+        <v>0.7269043922424316</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4692773818969727</v>
+        <v>0.461101770401001</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7205154895782471</v>
+        <v>0.7269043922424316</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.461101770401001</v>
+        <v>0.4664034843444824</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7269043922424316</v>
+        <v>0.7003335952758789</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.461101770401001</v>
+        <v>0.4664034843444824</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7269043922424316</v>
+        <v>0.7003335952758789</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4664034843444824</v>
+        <v>0.04841518402099609</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -503,11 +503,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.99375</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7003335952758789</v>
+        <v>0.05764937400817871</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -538,11 +538,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.99375</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4664034843444824</v>
+        <v>0.04841518402099609</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -634,11 +634,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.99375</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7003335952758789</v>
+        <v>0.05764937400817871</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -669,11 +669,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.99375</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04841518402099609</v>
+        <v>0.8451356887817383</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8998419434690367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9254890678941312</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8991261138706356</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9601233380302046</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05764937400817871</v>
+        <v>1.053424119949341</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9008461098105501</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9306674338319908</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9049920684579351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9450958342365778</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04841518402099609</v>
+        <v>0.8451356887817383</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8998419434690367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9254890678941312</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8991261138706356</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9601233380302046</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05764937400817871</v>
+        <v>1.053424119949341</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9008461098105501</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9306674338319908</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9049920684579351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9450958342365778</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8451356887817383</v>
+        <v>0.143366813659668</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8998419434690367</v>
+        <v>0.2911159827840349</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9254890678941312</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8991261138706356</v>
+        <v>0.367207148890009</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9601233380302046</v>
+        <v>0.8116088782451756</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.053424119949341</v>
+        <v>0.1354882717132568</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9008461098105501</v>
+        <v>0.2968661068732614</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9306674338319908</v>
+        <v>0.6030612244897959</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9049920684579351</v>
+        <v>0.3548945333884166</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9450958342365778</v>
+        <v>0.8013548174371788</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8451356887817383</v>
+        <v>0.143366813659668</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8998419434690367</v>
+        <v>0.2911159827840349</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9254890678941312</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8991261138706356</v>
+        <v>0.367207148890009</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9601233380302046</v>
+        <v>0.8116088782451756</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.053424119949341</v>
+        <v>0.1354882717132568</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9008461098105501</v>
+        <v>0.2968661068732614</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9306674338319908</v>
+        <v>0.6030612244897959</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9049920684579351</v>
+        <v>0.3548945333884166</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9450958342365778</v>
+        <v>0.8013548174371788</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.143366813659668</v>
+        <v>0.715111255645752</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2911159827840349</v>
+        <v>0.7178455340929982</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G2" t="n">
-        <v>0.367207148890009</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8116088782451756</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1354882717132568</v>
+        <v>1.173915863037109</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2968661068732614</v>
+        <v>0.7296280924933435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6030612244897959</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3548945333884166</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8013548174371788</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.143366813659668</v>
+        <v>0.715111255645752</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2911159827840349</v>
+        <v>0.7178455340929982</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G2" t="n">
-        <v>0.367207148890009</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8116088782451756</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1354882717132568</v>
+        <v>1.173915863037109</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2968661068732614</v>
+        <v>0.7296280924933435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6030612244897959</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3548945333884166</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8013548174371788</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.715111255645752</v>
+        <v>0.04831504821777344</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7178455340929982</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.173915863037109</v>
+        <v>0.06014561653137207</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7296280924933435</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.715111255645752</v>
+        <v>0.04831504821777344</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7178455340929982</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.173915863037109</v>
+        <v>0.06014561653137207</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7296280924933435</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04831504821777344</v>
+        <v>0.0374138355255127</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06014561653137207</v>
+        <v>0.04952788352966309</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04831504821777344</v>
+        <v>0.0374138355255127</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06014561653137207</v>
+        <v>0.04952788352966309</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0374138355255127</v>
+        <v>0.07305550575256348</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04952788352966309</v>
+        <v>0.04779195785522461</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -541,6 +541,41 @@
         <v>0.9999155405405405</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08679962158203125</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0374138355255127</v>
+        <v>0.07305550575256348</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04952788352966309</v>
+        <v>0.04779195785522461</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -672,6 +707,41 @@
         <v>0.9999155405405405</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08679962158203125</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07305550575256348</v>
+        <v>0.09245038032531738</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04779195785522461</v>
+        <v>0.07252597808837891</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08679962158203125</v>
+        <v>0.1275267601013184</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07305550575256348</v>
+        <v>0.09245038032531738</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04779195785522461</v>
+        <v>0.07252597808837891</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08679962158203125</v>
+        <v>0.1275267601013184</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09245038032531738</v>
+        <v>0.1134634017944336</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07252597808837891</v>
+        <v>0.07774615287780762</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1275267601013184</v>
+        <v>0.167536735534668</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09245038032531738</v>
+        <v>0.1134634017944336</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07252597808837891</v>
+        <v>0.07774615287780762</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1275267601013184</v>
+        <v>0.167536735534668</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1134634017944336</v>
+        <v>0.3354244232177734</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8998419434690367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9254890678941312</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8991261138706356</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9601233380302046</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07774615287780762</v>
+        <v>0.3668956756591797</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9008461098105501</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9306674338319908</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9049920684579351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9450958342365778</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.167536735534668</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9983535762483131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9999155405405405</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1134634017944336</v>
+        <v>0.3354244232177734</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8998419434690367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9254890678941312</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8991261138706356</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9601233380302046</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07774615287780762</v>
+        <v>0.3668956756591797</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9008461098105501</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9306674338319908</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9049920684579351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9450958342365778</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.167536735534668</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9983535762483131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9999155405405405</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3354244232177734</v>
+        <v>0.4246313571929932</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8998419434690367</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9254890678941312</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8991261138706356</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9601233380302046</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3668956756591797</v>
+        <v>0.5478055477142334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9008461098105501</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9306674338319908</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9049920684579351</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9450958342365778</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 6, 'max_features': None, 'max_depth': 6, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3354244232177734</v>
+        <v>0.4246313571929932</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8998419434690367</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9254890678941312</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8991261138706356</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9601233380302046</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3668956756591797</v>
+        <v>0.5478055477142334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9008461098105501</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9306674338319908</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9049920684579351</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9450958342365778</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 6, 'max_features': None, 'max_depth': 6, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4246313571929932</v>
+        <v>0.5122740268707275</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5478055477142334</v>
+        <v>0.6788384914398193</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4246313571929932</v>
+        <v>0.5122740268707275</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5478055477142334</v>
+        <v>0.6788384914398193</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5122740268707275</v>
+        <v>0.5657615661621094</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.7178455340929982</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6788384914398193</v>
+        <v>0.8688530921936035</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.7296280924933435</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 6, 'max_features': None, 'max_depth': 6, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5122740268707275</v>
+        <v>0.5657615661621094</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.7178455340929982</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6788384914398193</v>
+        <v>0.8688530921936035</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.7296280924933435</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 6, 'max_features': None, 'max_depth': 6, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5657615661621094</v>
+        <v>1.819243192672729</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7178455340929982</v>
+        <v>0.9207321669579768</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9440395015283329</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9333833423014269</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9545206207717516</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8688530921936035</v>
+        <v>2.692499399185181</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7296280924933435</v>
+        <v>0.9272708256612205</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9440395015283329</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9333833423014269</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9545206207717516</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5657615661621094</v>
+        <v>1.819243192672729</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7178455340929982</v>
+        <v>0.9207321669579768</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9440395015283329</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9333833423014269</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9545206207717516</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8688530921936035</v>
+        <v>2.692499399185181</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7296280924933435</v>
+        <v>0.9272708256612205</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9440395015283329</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9333833423014269</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9545206207717516</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.819243192672729</v>
+        <v>1.113904476165771</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9207321669579768</v>
+        <v>0.5120719056338662</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9440395015283329</v>
+        <v>0.8044084114517355</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9333833423014269</v>
+        <v>0.5491384742798635</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9545206207717516</v>
+        <v>0.8992762005533714</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.692499399185181</v>
+        <v>2.524046182632446</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9272708256612205</v>
+        <v>0.5277851553954449</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9440395015283329</v>
+        <v>0.7990879148720548</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9333833423014269</v>
+        <v>0.5342969532961104</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9545206207717516</v>
+        <v>0.9110942948206118</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.819243192672729</v>
+        <v>1.113904476165771</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9207321669579768</v>
+        <v>0.5120719056338662</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9440395015283329</v>
+        <v>0.8044084114517355</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9333833423014269</v>
+        <v>0.5491384742798635</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9545206207717516</v>
+        <v>0.8992762005533714</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.692499399185181</v>
+        <v>2.524046182632446</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9272708256612205</v>
+        <v>0.5277851553954449</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9440395015283329</v>
+        <v>0.7990879148720548</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9333833423014269</v>
+        <v>0.5342969532961104</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9545206207717516</v>
+        <v>0.9110942948206118</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.113904476165771</v>
+        <v>0.9261305332183838</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5120719056338662</v>
+        <v>0.3391992867247582</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8044084114517355</v>
+        <v>0.613265306122449</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5491384742798635</v>
+        <v>0.4332895651444917</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8992762005533714</v>
+        <v>0.7744047619047619</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.524046182632446</v>
+        <v>1.807075500488281</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5277851553954449</v>
+        <v>0.3503912807052719</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7990879148720548</v>
+        <v>0.613265306122449</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5342969532961104</v>
+        <v>0.4332895651444917</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9110942948206118</v>
+        <v>0.7744047619047619</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.113904476165771</v>
+        <v>0.9261305332183838</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5120719056338662</v>
+        <v>0.3391992867247582</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8044084114517355</v>
+        <v>0.613265306122449</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5491384742798635</v>
+        <v>0.4332895651444917</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8992762005533714</v>
+        <v>0.7744047619047619</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.524046182632446</v>
+        <v>1.807075500488281</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5277851553954449</v>
+        <v>0.3503912807052719</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7990879148720548</v>
+        <v>0.613265306122449</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5342969532961104</v>
+        <v>0.4332895651444917</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9110942948206118</v>
+        <v>0.7744047619047619</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9261305332183838</v>
+        <v>0.07559800148010254</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3391992867247582</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.613265306122449</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4332895651444917</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7744047619047619</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.807075500488281</v>
+        <v>0.08429169654846191</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3503912807052719</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.613265306122449</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4332895651444917</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7744047619047619</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1428027153015137</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9261305332183838</v>
+        <v>0.07559800148010254</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3391992867247582</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.613265306122449</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4332895651444917</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7744047619047619</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.807075500488281</v>
+        <v>0.08429169654846191</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3503912807052719</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.613265306122449</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4332895651444917</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7744047619047619</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1428027153015137</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07559800148010254</v>
+        <v>0.08355903625488281</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08429169654846191</v>
+        <v>0.07306814193725586</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1428027153015137</v>
+        <v>0.1751999855041504</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07559800148010254</v>
+        <v>0.08355903625488281</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08429169654846191</v>
+        <v>0.07306814193725586</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1428027153015137</v>
+        <v>0.1751999855041504</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08355903625488281</v>
+        <v>0.4917073249816895</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8877861070208095</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9097972972972973</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9003132051325229</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.938653824618658</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07306814193725586</v>
+        <v>0.9211866855621338</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.8862895625445848</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9097972972972973</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9003132051325229</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.938653824618658</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1751999855041504</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9983535762483131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9999155405405405</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08355903625488281</v>
+        <v>0.4917073249816895</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8877861070208095</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9097972972972973</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9003132051325229</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.938653824618658</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07306814193725586</v>
+        <v>0.9211866855621338</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.8862895625445848</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9097972972972973</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9003132051325229</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.938653824618658</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1751999855041504</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9983535762483131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9999155405405405</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4917073249816895</v>
+        <v>0.6341204643249512</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8877861070208095</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9097972972972973</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9003132051325229</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.938653824618658</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9211866855621338</v>
+        <v>0.9664053916931152</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8862895625445848</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9097972972972973</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9003132051325229</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.938653824618658</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4917073249816895</v>
+        <v>0.6341204643249512</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8877861070208095</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9097972972972973</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9003132051325229</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.938653824618658</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9211866855621338</v>
+        <v>0.9664053916931152</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8862895625445848</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9097972972972973</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9003132051325229</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.938653824618658</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6341204643249512</v>
+        <v>0.5360722541809082</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9664053916931152</v>
+        <v>0.6800587177276611</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6341204643249512</v>
+        <v>0.5360722541809082</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9664053916931152</v>
+        <v>0.6800587177276611</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
